--- a/sheets/조재수대금교본/검수/청성곡 (2).xlsx
+++ b/sheets/조재수대금교본/검수/청성곡 (2).xlsx
@@ -6688,16 +6688,16 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 㳞
-汰ʒ</t>
+汰</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃仲
-太ㄷ∽
+太
 –</t>
         </is>
       </c>
@@ -6712,7 +6712,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">И潢
+          <t xml:space="preserve">潢
 △
 –</t>
         </is>
@@ -6722,15 +6722,14 @@
         <is>
           <t xml:space="preserve">林∼
 –
-林∧
-‹</t>
+林</t>
         </is>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
-㳞汰∽
+          <t xml:space="preserve">汰潢
+㳞汰
 –</t>
         </is>
       </c>
@@ -6745,8 +6744,8 @@
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ʒ潢㳞
-汰∽
+          <t xml:space="preserve">潢㳞
+汰
 –</t>
         </is>
       </c>
@@ -6760,7 +6759,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -6774,7 +6773,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ㳞
+          <t xml:space="preserve">潢㳞
 汰
 –</t>
         </is>
@@ -6782,9 +6781,9 @@
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ
-–
-–И</t>
+          <t xml:space="preserve">林
+–
+–</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -6796,7 +6795,7 @@
         <is>
           <t xml:space="preserve">–∼
 –㳞
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="S4" s="23"/>
@@ -6805,25 +6804,21 @@
     </row>
     <row r="5" ht="157.03" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="24"/>
       <c r="D5" s="21"/>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И
+–
 黃△</t>
         </is>
       </c>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ʒ
+          <t xml:space="preserve">林
 仲
 –∼</t>
         </is>
@@ -6833,9 +6828,8 @@
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ
+          <t xml:space="preserve">林
 南
-ﾉ
 △</t>
         </is>
       </c>
@@ -6846,7 +6840,7 @@
       <c r="Q5" s="24"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ
+          <t xml:space="preserve">林
 △
 林</t>
         </is>
@@ -6870,18 +6864,16 @@
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-ﾉ
 黃∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ黃
+          <t xml:space="preserve">太黃
 黃
-–ㄴ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -6897,15 +6889,15 @@
         <is>
           <t xml:space="preserve">潢∼
 –
-∧汰㳞</t>
+汰㳞</t>
         </is>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰∧
-–⌝</t>
+–汰
+–</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -6916,8 +6908,7 @@
       <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–
-⌝</t>
+–</t>
         </is>
       </c>
       <c r="U6" s="22"/>
@@ -6936,7 +6927,7 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南ﾉ
+          <t xml:space="preserve">林南
 林
 –∼</t>
         </is>
@@ -6945,7 +6936,6 @@
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-ﾉ
 林∼
 –</t>
         </is>
@@ -6954,7 +6944,7 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ʒ
+潢
 南林</t>
         </is>
       </c>
@@ -6965,7 +6955,7 @@
         <is>
           <t xml:space="preserve">林∼
 –
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -6974,16 +6964,14 @@
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–∼
-ИИ</t>
+–∼</t>
         </is>
       </c>
       <c r="S7" s="23"/>
       <c r="T7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林∧
-–
-ㄴ</t>
+          <t xml:space="preserve">林
+–</t>
         </is>
       </c>
       <c r="U7" s="23"/>
@@ -6998,7 +6986,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -7006,7 +6994,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -7022,8 +7010,8 @@
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ㳞
-汰ʒ潢
+          <t xml:space="preserve">潢㳞
+汰潢
 △</t>
         </is>
       </c>
@@ -7034,15 +7022,15 @@
         <is>
           <t xml:space="preserve">仲
 –
-–ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="S8" s="24"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 㳞
-汰ʒ∽</t>
+汰</t>
         </is>
       </c>
       <c r="U8" s="24"/>
@@ -7057,25 +7045,22 @@
         <is>
           <t xml:space="preserve">林
 –
-–ㄴ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–∼
-И
-‹</t>
+–∼</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 㳞
-汰ʒ</t>
+汰</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -7083,7 +7068,7 @@
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
+          <t xml:space="preserve">汰潢
 –
 –</t>
         </is>
@@ -7093,9 +7078,9 @@
       <c r="Q9" s="22"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ黃∼
-–
-–И</t>
+          <t xml:space="preserve">太黃∼
+–
+–</t>
         </is>
       </c>
       <c r="S9" s="22"/>
@@ -7103,7 +7088,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="U9" s="22"/>
@@ -7117,14 +7102,14 @@
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢∼
-–И
+–
 汰㳞</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ʒ
+          <t xml:space="preserve">林
 潢
 –</t>
         </is>
@@ -7134,7 +7119,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="K10" s="23"/>
@@ -7154,7 +7139,7 @@
         <is>
           <t xml:space="preserve">仲·
 △
-仲太ㄷ</t>
+仲太</t>
         </is>
       </c>
       <c r="S10" s="23"/>
@@ -7169,7 +7154,7 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽
+          <t xml:space="preserve">汰
 –
 –</t>
         </is>
@@ -7195,7 +7180,7 @@
         <is>
           <t xml:space="preserve">–
 –
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="O11" s="24"/>
@@ -7230,7 +7215,7 @@
         <is>
           <t xml:space="preserve">–
 –㳞
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -7243,14 +7228,14 @@
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢㳞
-汰∽
+汰
 –</t>
         </is>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ʒ
+          <t xml:space="preserve">林
 仲∼
 –</t>
         </is>
@@ -7268,8 +7253,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="U12" s="22"/>
@@ -7284,13 +7268,13 @@
         <is>
           <t xml:space="preserve">汰
 –
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -7298,7 +7282,7 @@
         <is>
           <t xml:space="preserve">–
 –㳞
-汰⌝</t>
+汰</t>
         </is>
       </c>
       <c r="K13" s="23"/>
@@ -7306,29 +7290,25 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ
+          <t xml:space="preserve">太
 黃∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="O13" s="23"/>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–太∧
+–太
 黃△</t>
         </is>
       </c>
       <c r="S13" s="23"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="U13" s="23"/>
@@ -7343,16 +7323,15 @@
         <is>
           <t xml:space="preserve">林∼
 –
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И
-仲ﾉ
-‹</t>
+–
+仲</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -7360,8 +7339,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K14" s="24"/>
@@ -7373,9 +7351,9 @@
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南ﾉ
+          <t xml:space="preserve">林南
 林∼
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="O14" s="24"/>
@@ -7386,8 +7364,7 @@
       <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-–
-И</t>
+–</t>
         </is>
       </c>
       <c r="U14" s="24"/>
@@ -7445,7 +7422,6 @@
       <c r="T17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-ﾉ
 林
 –</t>
         </is>
@@ -7476,7 +7452,7 @@
         <is>
           <t xml:space="preserve">–
 –
-И太∽</t>
+太</t>
         </is>
       </c>
       <c r="U18" s="23"/>
@@ -7505,7 +7481,7 @@
         <is>
           <t xml:space="preserve">林∼
 –
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="U19" s="24"/>
@@ -7534,7 +7510,7 @@
         <is>
           <t xml:space="preserve">林∼
 潢
-∧汰㳞</t>
+汰㳞</t>
         </is>
       </c>
       <c r="U20" s="22"/>
@@ -7613,7 +7589,7 @@
       <c r="S23" s="22"/>
       <c r="T23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽
+          <t xml:space="preserve">汰
 △
 汰</t>
         </is>
@@ -7751,7 +7727,7 @@
       <c r="T28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∽汰潢
+汰潢
 △</t>
         </is>
       </c>
@@ -7791,7 +7767,7 @@
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧黃</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="C31" s="22"/>
@@ -7799,22 +7775,22 @@
         <is>
           <t xml:space="preserve">–
 潢南
-–ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 㳞
-汰ʒ</t>
+汰</t>
         </is>
       </c>
       <c r="G31" s="22"/>
       <c r="H31" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃仲
-太ㄷ∽
+太
 –</t>
         </is>
       </c>
@@ -7839,15 +7815,14 @@
         <is>
           <t xml:space="preserve">林
 –∼
-林∧
-‹</t>
+林</t>
         </is>
       </c>
       <c r="O31" s="22"/>
       <c r="P31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
-㳞汰∽
+          <t xml:space="preserve">汰潢
+㳞汰
 –</t>
         </is>
       </c>
@@ -7858,7 +7833,7 @@
         <is>
           <t xml:space="preserve">林
 –∼
-–И</t>
+–</t>
         </is>
       </c>
       <c r="U31" s="22"/>
@@ -7869,7 +7844,7 @@
       <c r="C32" s="23"/>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ʒ
+          <t xml:space="preserve">林
 仲∼
 –</t>
         </is>
@@ -7879,7 +7854,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="G32" s="23"/>
@@ -7893,7 +7868,7 @@
       <c r="K32" s="23"/>
       <c r="L32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ㳞
+          <t xml:space="preserve">潢㳞
 汰
 –</t>
         </is>
@@ -7901,9 +7876,9 @@
       <c r="M32" s="23"/>
       <c r="N32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ
-–
-–И</t>
+          <t xml:space="preserve">林
+–
+–</t>
         </is>
       </c>
       <c r="O32" s="23"/>
@@ -7926,7 +7901,7 @@
       <c r="C33" s="24"/>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ
+          <t xml:space="preserve">太
 黃∼
 –</t>
         </is>
@@ -7937,14 +7912,14 @@
       <c r="H33" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И
+–
 黃△</t>
         </is>
       </c>
       <c r="I33" s="24"/>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ʒ
+          <t xml:space="preserve">林
 仲
 –∼</t>
         </is>
@@ -7954,9 +7929,8 @@
       <c r="M33" s="24"/>
       <c r="N33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ
+          <t xml:space="preserve">林
 南
-ﾉ
 △</t>
         </is>
       </c>
@@ -7967,7 +7941,7 @@
       <c r="S33" s="24"/>
       <c r="T33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
+          <t xml:space="preserve">汰
 △
 汰</t>
         </is>
@@ -7980,7 +7954,7 @@
       <c r="C34" s="22"/>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–И
+          <t xml:space="preserve">–
 仲
 △</t>
         </is>
@@ -7991,18 +7965,16 @@
       <c r="H34" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-ﾉ
 黃∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="I34" s="22"/>
       <c r="J34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ黃
+          <t xml:space="preserve">太黃
 黃∼
-–ㄴ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K34" s="22"/>
@@ -8018,15 +7990,15 @@
         <is>
           <t xml:space="preserve">潢
 –∼
-∧汰㳞</t>
+汰㳞</t>
         </is>
       </c>
       <c r="O34" s="22"/>
       <c r="P34" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰∧
-–⌝</t>
+–汰
+–</t>
         </is>
       </c>
       <c r="Q34" s="22"/>
@@ -8045,7 +8017,7 @@
       <c r="C35" s="23"/>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲太ㄷ
+          <t xml:space="preserve">仲太
 –
 –</t>
         </is>
@@ -8062,7 +8034,6 @@
       <c r="H35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-ﾉ
 林
 –∼</t>
         </is>
@@ -8071,7 +8042,6 @@
       <c r="J35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-ﾉ
 林
 –∼</t>
         </is>
@@ -8080,7 +8050,7 @@
       <c r="L35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ʒ
+潢
 南林</t>
         </is>
       </c>
@@ -8091,7 +8061,7 @@
         <is>
           <t xml:space="preserve">林
 –∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="Q35" s="23"/>
@@ -8112,10 +8082,9 @@
       <c r="E36" s="24"/>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ
-–
-–
-ﾉ</t>
+          <t xml:space="preserve">南
+–
+–</t>
         </is>
       </c>
       <c r="G36" s="24"/>
@@ -8123,7 +8092,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="I36" s="24"/>
@@ -8131,7 +8100,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="K36" s="24"/>
@@ -8147,8 +8116,8 @@
       <c r="O36" s="24"/>
       <c r="P36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ㳞
-汰ʒ潢
+          <t xml:space="preserve">潢㳞
+汰潢
 △</t>
         </is>
       </c>
@@ -8169,14 +8138,14 @@
       <c r="D37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И
+–
 黃·</t>
         </is>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ИИ
+          <t xml:space="preserve">林
 仲
 –∼</t>
         </is>
@@ -8185,26 +8154,22 @@
       <c r="H37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–
-И
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I37" s="22"/>
       <c r="J37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–∼
-И
-‹</t>
+–∼</t>
         </is>
       </c>
       <c r="K37" s="22"/>
       <c r="L37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 㳞
-汰ʒ</t>
+汰</t>
         </is>
       </c>
       <c r="M37" s="22"/>
@@ -8212,7 +8177,7 @@
       <c r="O37" s="22"/>
       <c r="P37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∽汰潢
+          <t xml:space="preserve">汰潢
 –
 –</t>
         </is>
@@ -8243,7 +8208,7 @@
       <c r="E38" s="23"/>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ
+          <t xml:space="preserve">太
 黃
 –∼</t>
         </is>
@@ -8252,14 +8217,14 @@
       <c r="H38" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢∼
-–И
+–
 汰㳞</t>
         </is>
       </c>
       <c r="I38" s="23"/>
       <c r="J38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ʒ
+          <t xml:space="preserve">林
 潢
 –</t>
         </is>
@@ -8269,7 +8234,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-∽汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="M38" s="23"/>
@@ -8296,22 +8261,20 @@
         <is>
           <t xml:space="preserve">–
 –∼
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="E39" s="24"/>
       <c r="F39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–
-ㄴ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G39" s="24"/>
       <c r="H39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽
+          <t xml:space="preserve">汰
 –
 –</t>
         </is>
@@ -8333,7 +8296,7 @@
         <is>
           <t xml:space="preserve">–
 –
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="Q39" s="24"/>
@@ -8350,7 +8313,7 @@
         <is>
           <t xml:space="preserve">林∼
 –
-ㄴ·</t>
+·</t>
         </is>
       </c>
       <c r="E40" s="22"/>
@@ -8358,7 +8321,7 @@
         <is>
           <t xml:space="preserve">林南
 林
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="G40" s="22"/>
@@ -8387,14 +8350,14 @@
       <c r="N40" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢㳞
-汰∽
+汰
 –</t>
         </is>
       </c>
       <c r="O40" s="22"/>
       <c r="P40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ʒ
+          <t xml:space="preserve">林
 仲
 –∼</t>
         </is>
@@ -8407,16 +8370,12 @@
     </row>
     <row r="41" ht="157.03" customHeight="true">
       <c r="A41" s="0"/>
-      <c r="B41" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">∽</t>
-        </is>
-      </c>
+      <c r="B41" s="21"/>
       <c r="C41" s="23"/>
       <c r="D41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林仲
-ﾉ∼
+∼
 太黃仲</t>
         </is>
       </c>
@@ -8424,23 +8383,21 @@
       <c r="F41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–
-И
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G41" s="23"/>
       <c r="H41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ʒ
+潢
 南林</t>
         </is>
       </c>
       <c r="I41" s="23"/>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄷ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K41" s="23"/>
@@ -8448,7 +8405,7 @@
         <is>
           <t xml:space="preserve">–
 –㳞
-汰⌝</t>
+汰</t>
         </is>
       </c>
       <c r="M41" s="23"/>
@@ -8456,16 +8413,15 @@
       <c r="O41" s="23"/>
       <c r="P41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ
+          <t xml:space="preserve">太
 黃
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="Q41" s="23"/>
       <c r="R41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="S41" s="23"/>
@@ -8478,7 +8434,7 @@
       <c r="C42" s="24"/>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ʒ∽
+          <t xml:space="preserve">太
 黃·
 △</t>
         </is>
@@ -8503,8 +8459,8 @@
       <c r="J42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И
-仲ﾉ</t>
+–
+仲</t>
         </is>
       </c>
       <c r="K42" s="24"/>
@@ -8512,8 +8468,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–ﾉ
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M42" s="24"/>
@@ -8526,9 +8481,8 @@
       <c r="P42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-ﾉ
 林∼
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="Q42" s="24"/>

--- a/sheets/조재수대금교본/검수/청성곡 (2).xlsx
+++ b/sheets/조재수대금교본/검수/청성곡 (2).xlsx
@@ -6688,16 +6688,16 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 㳞
-汰</t>
+汰ʒ</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃仲
-太
+太ㄷ∽
 –</t>
         </is>
       </c>
@@ -6712,7 +6712,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">И潢
 △
 –</t>
         </is>
@@ -6722,14 +6722,14 @@
         <is>
           <t xml:space="preserve">林∼
 –
-林</t>
+林∧</t>
         </is>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
-㳞汰
+          <t xml:space="preserve">∽汰潢
+㳞汰∽
 –</t>
         </is>
       </c>
@@ -6744,8 +6744,8 @@
       <c r="S3" s="22"/>
       <c r="T3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞
-汰
+          <t xml:space="preserve">ʒ潢㳞
+汰∽
 –</t>
         </is>
       </c>
@@ -6759,7 +6759,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -6773,7 +6773,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞
+          <t xml:space="preserve">潢ʒ㳞
 汰
 –</t>
         </is>
@@ -6781,9 +6781,9 @@
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-–
-–</t>
+          <t xml:space="preserve">林ㄷ
+–
+–И</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -6795,7 +6795,7 @@
         <is>
           <t xml:space="preserve">–∼
 –㳞
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="S4" s="23"/>
@@ -6811,14 +6811,14 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–
+–И
 黃△</t>
         </is>
       </c>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ʒ
 仲
 –∼</t>
         </is>
@@ -6828,8 +6828,9 @@
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ㄷ
 南
+ﾉ
 △</t>
         </is>
       </c>
@@ -6840,7 +6841,7 @@
       <c r="Q5" s="24"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ㄷ
 △
 林</t>
         </is>
@@ -6864,16 +6865,17 @@
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
+ﾉ
 黃∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太黃
+          <t xml:space="preserve">太ʒ黃
 黃
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -6889,15 +6891,15 @@
         <is>
           <t xml:space="preserve">潢∼
 –
-汰㳞</t>
+∧汰㳞</t>
         </is>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰
-–</t>
+–汰∧
+–⌝</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -6908,7 +6910,8 @@
       <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–
+⌝</t>
         </is>
       </c>
       <c r="U6" s="22"/>
@@ -6927,7 +6930,7 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
+          <t xml:space="preserve">林南ﾉ
 林
 –∼</t>
         </is>
@@ -6936,6 +6939,7 @@
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
+ﾉ
 林∼
 –</t>
         </is>
@@ -6944,7 +6948,7 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
+潢ʒ
 南林</t>
         </is>
       </c>
@@ -6955,7 +6959,7 @@
         <is>
           <t xml:space="preserve">林∼
 –
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -6964,14 +6968,16 @@
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–∼</t>
+–∼
+ИИ</t>
         </is>
       </c>
       <c r="S7" s="23"/>
       <c r="T7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-–</t>
+          <t xml:space="preserve">林∧
+–
+ㄴ</t>
         </is>
       </c>
       <c r="U7" s="23"/>
@@ -6986,7 +6992,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -6994,7 +7000,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -7010,8 +7016,8 @@
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞
-汰潢
+          <t xml:space="preserve">潢ʒ㳞
+汰ʒ潢
 △</t>
         </is>
       </c>
@@ -7022,15 +7028,15 @@
         <is>
           <t xml:space="preserve">仲
 –
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="S8" s="24"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 㳞
-汰</t>
+汰ʒ∽</t>
         </is>
       </c>
       <c r="U8" s="24"/>
@@ -7045,22 +7051,23 @@
         <is>
           <t xml:space="preserve">林
 –
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–∼</t>
+–∼
+И</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 㳞
-汰</t>
+汰ʒ</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -7068,7 +7075,7 @@
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">∽汰潢
 –
 –</t>
         </is>
@@ -7078,9 +7085,9 @@
       <c r="Q9" s="22"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太黃∼
-–
-–</t>
+          <t xml:space="preserve">太ʒ黃∼
+–
+–И</t>
         </is>
       </c>
       <c r="S9" s="22"/>
@@ -7088,7 +7095,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="U9" s="22"/>
@@ -7102,14 +7109,14 @@
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢∼
-–
+–И
 汰㳞</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ʒ
 潢
 –</t>
         </is>
@@ -7119,7 +7126,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="K10" s="23"/>
@@ -7139,7 +7146,7 @@
         <is>
           <t xml:space="preserve">仲·
 △
-仲太</t>
+仲太ㄷ</t>
         </is>
       </c>
       <c r="S10" s="23"/>
@@ -7154,7 +7161,7 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∽
 –
 –</t>
         </is>
@@ -7180,7 +7187,7 @@
         <is>
           <t xml:space="preserve">–
 –
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="O11" s="24"/>
@@ -7215,7 +7222,7 @@
         <is>
           <t xml:space="preserve">–
 –㳞
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -7228,14 +7235,14 @@
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢㳞
-汰
+汰∽
 –</t>
         </is>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ʒ
 仲∼
 –</t>
         </is>
@@ -7253,7 +7260,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="U12" s="22"/>
@@ -7268,13 +7275,13 @@
         <is>
           <t xml:space="preserve">汰
 –
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㄷ</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -7282,7 +7289,7 @@
         <is>
           <t xml:space="preserve">–
 –㳞
-汰</t>
+汰⌝</t>
         </is>
       </c>
       <c r="K13" s="23"/>
@@ -7290,9 +7297,9 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ʒ
 黃∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -7301,14 +7308,14 @@
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–太
+–太∧
 黃△</t>
         </is>
       </c>
       <c r="S13" s="23"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㄷ</t>
         </is>
       </c>
       <c r="U13" s="23"/>
@@ -7323,15 +7330,15 @@
         <is>
           <t xml:space="preserve">林∼
 –
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–
-仲</t>
+–И
+仲ﾉ</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -7339,7 +7346,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="K14" s="24"/>
@@ -7351,9 +7358,9 @@
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
+          <t xml:space="preserve">林南ﾉ
 林∼
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="O14" s="24"/>
@@ -7364,7 +7371,8 @@
       <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-–</t>
+–
+И</t>
         </is>
       </c>
       <c r="U14" s="24"/>
@@ -7422,6 +7430,7 @@
       <c r="T17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
+ﾉ
 林
 –</t>
         </is>
@@ -7452,7 +7461,7 @@
         <is>
           <t xml:space="preserve">–
 –
-太</t>
+И太∽</t>
         </is>
       </c>
       <c r="U18" s="23"/>
@@ -7481,7 +7490,7 @@
         <is>
           <t xml:space="preserve">林∼
 –
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="U19" s="24"/>
@@ -7510,7 +7519,7 @@
         <is>
           <t xml:space="preserve">林∼
 潢
-汰㳞</t>
+∧汰㳞</t>
         </is>
       </c>
       <c r="U20" s="22"/>
@@ -7589,7 +7598,7 @@
       <c r="S23" s="22"/>
       <c r="T23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∽
 △
 汰</t>
         </is>
@@ -7727,7 +7736,7 @@
       <c r="T28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰潢
+∽汰潢
 △</t>
         </is>
       </c>
@@ -7767,7 +7776,7 @@
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">∧黃</t>
         </is>
       </c>
       <c r="C31" s="22"/>
@@ -7775,22 +7784,22 @@
         <is>
           <t xml:space="preserve">–
 潢南
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 㳞
-汰</t>
+汰ʒ</t>
         </is>
       </c>
       <c r="G31" s="22"/>
       <c r="H31" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太黃仲
-太
+太ㄷ∽
 –</t>
         </is>
       </c>
@@ -7815,14 +7824,14 @@
         <is>
           <t xml:space="preserve">林
 –∼
-林</t>
+林∧</t>
         </is>
       </c>
       <c r="O31" s="22"/>
       <c r="P31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
-㳞汰
+          <t xml:space="preserve">∽汰潢
+㳞汰∽
 –</t>
         </is>
       </c>
@@ -7833,7 +7842,7 @@
         <is>
           <t xml:space="preserve">林
 –∼
-–</t>
+–И</t>
         </is>
       </c>
       <c r="U31" s="22"/>
@@ -7844,7 +7853,7 @@
       <c r="C32" s="23"/>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ʒ
 仲∼
 –</t>
         </is>
@@ -7854,7 +7863,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="G32" s="23"/>
@@ -7868,7 +7877,7 @@
       <c r="K32" s="23"/>
       <c r="L32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞
+          <t xml:space="preserve">潢ʒ㳞
 汰
 –</t>
         </is>
@@ -7876,9 +7885,9 @@
       <c r="M32" s="23"/>
       <c r="N32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-–
-–</t>
+          <t xml:space="preserve">林ㄷ
+–
+–И</t>
         </is>
       </c>
       <c r="O32" s="23"/>
@@ -7901,7 +7910,7 @@
       <c r="C33" s="24"/>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ʒ
 黃∼
 –</t>
         </is>
@@ -7912,14 +7921,14 @@
       <c r="H33" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–
+–И
 黃△</t>
         </is>
       </c>
       <c r="I33" s="24"/>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ʒ
 仲
 –∼</t>
         </is>
@@ -7929,8 +7938,9 @@
       <c r="M33" s="24"/>
       <c r="N33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ㄷ
 南
+ﾉ
 △</t>
         </is>
       </c>
@@ -7941,7 +7951,7 @@
       <c r="S33" s="24"/>
       <c r="T33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∧
 △
 汰</t>
         </is>
@@ -7954,7 +7964,7 @@
       <c r="C34" s="22"/>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">–И
 仲
 △</t>
         </is>
@@ -7965,16 +7975,17 @@
       <c r="H34" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
+ﾉ
 黃∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="I34" s="22"/>
       <c r="J34" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太黃
+          <t xml:space="preserve">太ʒ黃
 黃∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="K34" s="22"/>
@@ -7990,15 +8001,15 @@
         <is>
           <t xml:space="preserve">潢
 –∼
-汰㳞</t>
+∧汰㳞</t>
         </is>
       </c>
       <c r="O34" s="22"/>
       <c r="P34" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–汰
-–</t>
+–汰∧
+–⌝</t>
         </is>
       </c>
       <c r="Q34" s="22"/>
@@ -8017,7 +8028,7 @@
       <c r="C35" s="23"/>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲太
+          <t xml:space="preserve">仲太ㄷ
 –
 –</t>
         </is>
@@ -8034,6 +8045,7 @@
       <c r="H35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
+ﾉ
 林
 –∼</t>
         </is>
@@ -8042,6 +8054,7 @@
       <c r="J35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
+ﾉ
 林
 –∼</t>
         </is>
@@ -8050,7 +8063,7 @@
       <c r="L35" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
+潢ʒ
 南林</t>
         </is>
       </c>
@@ -8061,7 +8074,7 @@
         <is>
           <t xml:space="preserve">林
 –∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="Q35" s="23"/>
@@ -8082,9 +8095,10 @@
       <c r="E36" s="24"/>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-–
-–</t>
+          <t xml:space="preserve">南ㄱ
+–
+–
+ﾉ</t>
         </is>
       </c>
       <c r="G36" s="24"/>
@@ -8092,7 +8106,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="I36" s="24"/>
@@ -8100,7 +8114,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="K36" s="24"/>
@@ -8116,8 +8130,8 @@
       <c r="O36" s="24"/>
       <c r="P36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢㳞
-汰潢
+          <t xml:space="preserve">潢ʒ㳞
+汰ʒ潢
 △</t>
         </is>
       </c>
@@ -8138,14 +8152,14 @@
       <c r="D37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–
+–И
 黃·</t>
         </is>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ИИ
 仲
 –∼</t>
         </is>
@@ -8154,22 +8168,24 @@
       <c r="H37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–</t>
+–
+И</t>
         </is>
       </c>
       <c r="I37" s="22"/>
       <c r="J37" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–∼</t>
+–∼
+И</t>
         </is>
       </c>
       <c r="K37" s="22"/>
       <c r="L37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 㳞
-汰</t>
+汰ʒ</t>
         </is>
       </c>
       <c r="M37" s="22"/>
@@ -8177,7 +8193,7 @@
       <c r="O37" s="22"/>
       <c r="P37" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">∽汰潢
 –
 –</t>
         </is>
@@ -8208,7 +8224,7 @@
       <c r="E38" s="23"/>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ʒ
 黃
 –∼</t>
         </is>
@@ -8217,14 +8233,14 @@
       <c r="H38" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢∼
-–
+–И
 汰㳞</t>
         </is>
       </c>
       <c r="I38" s="23"/>
       <c r="J38" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ʒ
 潢
 –</t>
         </is>
@@ -8234,7 +8250,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-汰潢</t>
+∽汰潢</t>
         </is>
       </c>
       <c r="M38" s="23"/>
@@ -8261,20 +8277,21 @@
         <is>
           <t xml:space="preserve">–
 –∼
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="E39" s="24"/>
       <c r="F39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–
+ㄴ</t>
         </is>
       </c>
       <c r="G39" s="24"/>
       <c r="H39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∽
 –
 –</t>
         </is>
@@ -8296,7 +8313,7 @@
         <is>
           <t xml:space="preserve">–
 –
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="Q39" s="24"/>
@@ -8313,7 +8330,7 @@
         <is>
           <t xml:space="preserve">林∼
 –
-·</t>
+ㄴ·</t>
         </is>
       </c>
       <c r="E40" s="22"/>
@@ -8321,7 +8338,7 @@
         <is>
           <t xml:space="preserve">林南
 林
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="G40" s="22"/>
@@ -8350,14 +8367,14 @@
       <c r="N40" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢㳞
-汰
+汰∽
 –</t>
         </is>
       </c>
       <c r="O40" s="22"/>
       <c r="P40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ʒ
 仲
 –∼</t>
         </is>
@@ -8370,12 +8387,16 @@
     </row>
     <row r="41" ht="157.03" customHeight="true">
       <c r="A41" s="0"/>
-      <c r="B41" s="21"/>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∽</t>
+        </is>
+      </c>
       <c r="C41" s="23"/>
       <c r="D41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林仲
-∼
+ﾉ∼
 太黃仲</t>
         </is>
       </c>
@@ -8383,21 +8404,22 @@
       <c r="F41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–</t>
+–
+И</t>
         </is>
       </c>
       <c r="G41" s="23"/>
       <c r="H41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
+潢ʒ
 南林</t>
         </is>
       </c>
       <c r="I41" s="23"/>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㄷ</t>
         </is>
       </c>
       <c r="K41" s="23"/>
@@ -8405,7 +8427,7 @@
         <is>
           <t xml:space="preserve">–
 –㳞
-汰</t>
+汰⌝</t>
         </is>
       </c>
       <c r="M41" s="23"/>
@@ -8413,9 +8435,9 @@
       <c r="O41" s="23"/>
       <c r="P41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ʒ
 黃
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="Q41" s="23"/>
@@ -8434,7 +8456,7 @@
       <c r="C42" s="24"/>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ʒ∽
 黃·
 △</t>
         </is>
@@ -8459,8 +8481,8 @@
       <c r="J42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–
-仲</t>
+–И
+仲ﾉ</t>
         </is>
       </c>
       <c r="K42" s="24"/>
@@ -8468,7 +8490,7 @@
         <is>
           <t xml:space="preserve">南
 –
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="M42" s="24"/>
@@ -8481,8 +8503,9 @@
       <c r="P42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
+ﾉ
 林∼
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="Q42" s="24"/>

--- a/sheets/조재수대금교본/검수/청성곡 (2).xlsx
+++ b/sheets/조재수대금교본/검수/청성곡 (2).xlsx
@@ -6630,25 +6630,25 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.2" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="16.2" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.2" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="16.2" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="16.2" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="16.2" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
